--- a/data/trans_orig/P19C10_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C10_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por dolor de mandíbula / solo 2023 en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>10252</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>378792</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293026</t>
+          <t>293549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302413</t>
+          <t>302453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>677108</t>
+          <t>676736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>685863</t>
+          <t>685870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11200</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391151</t>
+          <t>394719</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>493635</t>
+          <t>494094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>892843</t>
+          <t>891184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>901879</t>
+          <t>901769</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,97%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511008</t>
+          <t>511759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522716</t>
+          <t>522699</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>526816</t>
+          <t>527380</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1039869</t>
+          <t>1041012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1053173</t>
+          <t>1053345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7902</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12094</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>855026</t>
+          <t>853852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>691653</t>
+          <t>691562</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698885</t>
+          <t>698619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1551425</t>
+          <t>1550218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1560919</t>
+          <t>1560850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>544954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>528348</t>
+          <t>529098</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>533885</t>
+          <t>533958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1075317</t>
+          <t>1074794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1080509</t>
+          <t>1080412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,77 +2465,77 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2809</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7625</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>3286</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6434</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>0,67%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2809</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6891</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>3286</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>1136</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>7457</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356951</t>
+          <t>356913</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2573,82 +2573,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>99,32%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>597100</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>592284</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>599367</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>955976</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>952828</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>958531</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>99,33%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>802</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>597100</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>593018</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>599366</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1357</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>955976</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>951805</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>958126</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271803</t>
+          <t>272406</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>401083</t>
+          <t>400856</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>406992</t>
+          <t>406825</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>675017</t>
+          <t>675376</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>681900</t>
+          <t>681810</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>13498</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29381</t>
+          <t>28889</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20987</t>
+          <t>21345</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>42989</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3335268</t>
+          <t>3334420</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3350039</t>
+          <t>3349189</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3549446</t>
+          <t>3549938</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3565630</t>
+          <t>3565329</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6890059</t>
+          <t>6891140</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6912061</t>
+          <t>6911703</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C10_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C10_2023-Edad-trans_orig.xlsx
@@ -760,22 +760,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>299978</t>
+          <t>339363</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293549</t>
+          <t>332640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302453</t>
+          <t>342020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>683425</t>
+          <t>718217</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676736</t>
+          <t>711629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>685870</t>
+          <t>720902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>400708</t>
+          <t>444051</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>394719</t>
+          <t>437369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>498485</t>
+          <t>480462</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>494094</t>
+          <t>476139</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>899192</t>
+          <t>924513</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>891184</t>
+          <t>915558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>901769</t>
+          <t>927432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518820</t>
+          <t>595933</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511759</t>
+          <t>588121</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522699</t>
+          <t>599801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>530419</t>
+          <t>605748</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>527380</t>
+          <t>601942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1049239</t>
+          <t>1201680</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1041012</t>
+          <t>1194593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1053345</t>
+          <t>1206176</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>524042</t>
+          <t>601124</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1055923</t>
+          <t>1208405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1779,77 +1779,77 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5409</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2591</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10022</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>7676</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>4137</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>14632</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>1,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4331</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9030</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>6555</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2669</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>13301</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1867,102 +1867,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>860704</t>
+          <t>676031</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853852</t>
+          <t>670401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>716348</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>711735</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>719166</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1748</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1392380</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1385424</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1395919</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>98,95%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1109</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>696261</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>691562</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>698619</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1748</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1556964</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1550218</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1560850</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,22 +2167,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>532088</t>
+          <t>593214</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>529098</t>
+          <t>589588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>533958</t>
+          <t>595243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1078667</t>
+          <t>1186569</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1074794</t>
+          <t>1182505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1080412</t>
+          <t>1188486</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>534526</t>
+          <t>595849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1081105</t>
+          <t>1189204</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>500</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>358876</t>
+          <t>397244</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>356913</t>
+          <t>394727</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>597100</t>
+          <t>425788</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>592284</t>
+          <t>422117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>599367</t>
+          <t>427716</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>955976</t>
+          <t>823032</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>952828</t>
+          <t>819046</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>958531</t>
+          <t>825383</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>955</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>274810</t>
+          <t>301454</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>272406</t>
+          <t>297701</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>404636</t>
+          <t>441541</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>400856</t>
+          <t>437446</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>406825</t>
+          <t>443823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>679446</t>
+          <t>742996</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>675376</t>
+          <t>737991</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>681810</t>
+          <t>745438</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,22 +3126,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19801</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28889</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41908</t>
+          <t>46626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -3239,27 +3239,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3343944</t>
+          <t>3386923</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3334420</t>
+          <t>3377137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3349189</t>
+          <t>3392659</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3558965</t>
+          <t>3602464</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3549938</t>
+          <t>3592411</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3565329</t>
+          <t>3609717</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6902909</t>
+          <t>6989386</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6891140</t>
+          <t>6976499</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6911703</t>
+          <t>6998740</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
